--- a/SAP Reports/Input Files/P&L Jan 26/PL CHALLPG JAN 26 ANNUAL.xlsx
+++ b/SAP Reports/Input Files/P&L Jan 26/PL CHALLPG JAN 26 ANNUAL.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="143">
   <si>
     <t>Account Name</t>
   </si>
@@ -28,7 +28,7 @@
     <t>Revenues</t>
   </si>
   <si>
-    <t>$  1,540,902.40</t>
+    <t>$  1,501,116.46</t>
   </si>
   <si>
     <t>Income - Income</t>
@@ -37,12 +37,27 @@
     <t>Sales Revenue - SALES REVENUE</t>
   </si>
   <si>
-    <t>$  1,513,619.00</t>
+    <t>$  1,490,991.36</t>
   </si>
   <si>
     <t>480100-02-000-00 - REV-HOURS  INCOME</t>
   </si>
   <si>
+    <t>$  1,513,619.25</t>
+  </si>
+  <si>
+    <t>480140-02-000-00 - SHARE LDS/DISINCENTIVE</t>
+  </si>
+  <si>
+    <t>$ (21,077.89)</t>
+  </si>
+  <si>
+    <t>480150-02-000-00 - INDIVIDUAL LDS/DISINCENTIVE</t>
+  </si>
+  <si>
+    <t>$ (1,550.00)</t>
+  </si>
+  <si>
     <t>__________________</t>
   </si>
   <si>
@@ -55,7 +70,7 @@
     <t>Other Revenue - OTHER REVENUE</t>
   </si>
   <si>
-    <t>$  27,283.40</t>
+    <t>$  10,125.10</t>
   </si>
   <si>
     <t>480610-02-000-00 - DRIVER COPAY INCOME</t>
@@ -64,7 +79,13 @@
     <t>$  25,317.14</t>
   </si>
   <si>
-    <t>480800-02-000-00 - REPAIR SHOP INCOME</t>
+    <t>480620-02-000-00 - WMATA COPAY DEDUCTION</t>
+  </si>
+  <si>
+    <t>$ (17,158.30)</t>
+  </si>
+  <si>
+    <t>480800-02-000-00 - SHOP REPAIR INCOME</t>
   </si>
   <si>
     <t>$  1,966.26</t>
@@ -106,13 +127,13 @@
     <t>Gross Profit</t>
   </si>
   <si>
-    <t>$  1,541,002.40</t>
+    <t>$  1,501,216.46</t>
   </si>
   <si>
     <t>Expenses</t>
   </si>
   <si>
-    <t>$ (1,298,282.15)</t>
+    <t>$ (1,300,696.15)</t>
   </si>
   <si>
     <t>General Expense - General Expenses</t>
@@ -121,7 +142,7 @@
     <t>Payroll Expense - PAYROLL EXPENSE</t>
   </si>
   <si>
-    <t>$ (1,201,535.71)</t>
+    <t>$ (1,203,949.71)</t>
   </si>
   <si>
     <t>600014-02-000-00 - PAYROLL TAX:EMPLOYER</t>
@@ -190,7 +211,7 @@
     <t>$ (1,998.02)</t>
   </si>
   <si>
-    <t>600023-02-000-00 - SALARY ACCRUAL</t>
+    <t>600023-02-000-00 - WAGES PAYABLES</t>
   </si>
   <si>
     <t>$  423,174.29</t>
@@ -214,6 +235,12 @@
     <t>$ (7,482.87)</t>
   </si>
   <si>
+    <t>600140-02-000-00 - JANITORIAL SERVICE</t>
+  </si>
+  <si>
+    <t>$ (2,414.00)</t>
+  </si>
+  <si>
     <t>Total Payroll Expense - PAYROLL EXPENSE</t>
   </si>
   <si>
@@ -241,7 +268,7 @@
     <t>$ (9,462.43)</t>
   </si>
   <si>
-    <t>600032-02-000-00 - BANK SERVICE CHARGES</t>
+    <t>600032-02-000-00 - BANK CHARGES</t>
   </si>
   <si>
     <t>$ (37.77)</t>
@@ -364,15 +391,12 @@
     <t>Operating Profit</t>
   </si>
   <si>
-    <t>$  242,720.25</t>
+    <t>$  200,520.31</t>
   </si>
   <si>
     <t>FINANCE</t>
   </si>
   <si>
-    <t>$ (2,414.00)</t>
-  </si>
-  <si>
     <t>Depre &amp; Inc tax - INTEREST, TAX, DEPRECIATION, AMORTIZATION</t>
   </si>
   <si>
@@ -385,9 +409,6 @@
     <t>Income tax - INCOME TAX EXPENSE</t>
   </si>
   <si>
-    <t>600140-02-000-00 - JANITORIAL SERVICE</t>
-  </si>
-  <si>
     <t>Total Income tax - INCOME TAX EXPENSE</t>
   </si>
   <si>
@@ -398,9 +419,6 @@
   </si>
   <si>
     <t>Profit After Financing Expenses</t>
-  </si>
-  <si>
-    <t>$  240,306.25</t>
   </si>
   <si>
     <t>Other Revenues and Expenses</t>
@@ -1327,141 +1345,147 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C10" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
-		</row>
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" t="s">
+        <v>7</v>
+      </c>
+    </row>
     <row r="13">
-      <c r="A13" t="s">
-        <v>12</v>
-      </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="14">
 		</row>
     <row r="15">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" t="s">
-        <v>17</v>
-      </c>
-      <c r="C16" t="s">
-        <v>17</v>
-      </c>
-    </row>
+		</row>
     <row r="17">
+      <c r="A17" t="s">
+        <v>19</v>
+      </c>
       <c r="B17" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B18" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="C19" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="B21" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C21" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C22" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B24" t="s">
         <v>4</v>
@@ -1471,1099 +1495,1090 @@
       </c>
     </row>
     <row r="25">
-		</row>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>16</v>
+      </c>
+    </row>
     <row r="26">
-      <c r="A26" t="s">
-        <v>21</v>
-      </c>
       <c r="B26" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
     </row>
     <row r="27">
-		</row>
+      <c r="A27" t="s">
+        <v>27</v>
+      </c>
+      <c r="B27" t="s">
+        <v>4</v>
+      </c>
+      <c r="C27" t="s">
+        <v>4</v>
+      </c>
+    </row>
     <row r="28">
-      <c r="A28" t="s">
-        <v>23</v>
-      </c>
-      <c r="B28" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" t="s">
-        <v>22</v>
-      </c>
-    </row>
+		</row>
     <row r="29">
-		</row>
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>29</v>
+      </c>
+      <c r="C29" t="s">
+        <v>29</v>
+      </c>
+    </row>
     <row r="30">
-      <c r="A30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" t="s">
-        <v>22</v>
-      </c>
-      <c r="C30" t="s">
-        <v>22</v>
-      </c>
-    </row>
+		</row>
     <row r="31">
-		</row>
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" t="s">
+        <v>29</v>
+      </c>
+    </row>
     <row r="32">
-      <c r="A32" t="s">
-        <v>25</v>
-      </c>
-      <c r="B32" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" t="s">
-        <v>22</v>
-      </c>
-    </row>
+		</row>
     <row r="33">
+      <c r="A33" t="s">
+        <v>31</v>
+      </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C33" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="s">
-        <v>26</v>
-      </c>
-      <c r="B34" t="s">
-        <v>22</v>
-      </c>
-      <c r="C34" t="s">
-        <v>22</v>
-      </c>
-    </row>
+		</row>
     <row r="35">
+      <c r="A35" t="s">
+        <v>32</v>
+      </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="C35" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C36" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B37" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C37" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C38" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C39" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="B40" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C40" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
     </row>
     <row r="41">
-		</row>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="s">
+        <v>16</v>
+      </c>
+    </row>
     <row r="42">
       <c r="B42" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C42" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
+        <v>35</v>
+      </c>
+      <c r="B43" t="s">
         <v>29</v>
       </c>
-      <c r="B43" t="s">
-        <v>30</v>
-      </c>
       <c r="C43" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="s">
-        <v>31</v>
-      </c>
-      <c r="B44" t="s">
-        <v>32</v>
-      </c>
-      <c r="C44" t="s">
-        <v>32</v>
-      </c>
-    </row>
+		</row>
     <row r="45">
-		</row>
+      <c r="B45" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" t="s">
+        <v>14</v>
+      </c>
+    </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B46" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="C46" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="47">
-		</row>
+      <c r="A47" t="s">
+        <v>38</v>
+      </c>
+      <c r="B47" t="s">
+        <v>39</v>
+      </c>
+      <c r="C47" t="s">
+        <v>39</v>
+      </c>
+    </row>
     <row r="48">
-      <c r="A48" t="s">
-        <v>34</v>
-      </c>
-      <c r="B48" t="s">
-        <v>35</v>
-      </c>
-      <c r="C48" t="s">
-        <v>35</v>
-      </c>
-    </row>
+		</row>
     <row r="49">
-		</row>
+      <c r="A49" t="s">
+        <v>40</v>
+      </c>
+      <c r="B49" t="s">
+        <v>39</v>
+      </c>
+      <c r="C49" t="s">
+        <v>39</v>
+      </c>
+    </row>
     <row r="50">
-      <c r="A50" t="s">
-        <v>36</v>
-      </c>
-      <c r="B50" t="s">
-        <v>37</v>
-      </c>
-      <c r="C50" t="s">
-        <v>37</v>
-      </c>
-    </row>
+		</row>
     <row r="51">
       <c r="A51" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B51" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C51" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="s">
-        <v>40</v>
-      </c>
-      <c r="B52" t="s">
-        <v>41</v>
-      </c>
-      <c r="C52" t="s">
-        <v>41</v>
-      </c>
-    </row>
+		</row>
     <row r="53">
       <c r="A53" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B53" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C53" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B54" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C54" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B55" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C55" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B56" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C56" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B57" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C57" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B58" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C58" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B59" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C59" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B60" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C61" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C62" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B63" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C63" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B64" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C64" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="s">
+        <v>67</v>
+      </c>
       <c r="B65" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="C65" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B66" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="C66" t="s">
-        <v>35</v>
+        <v>70</v>
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="s">
+        <v>71</v>
+      </c>
       <c r="B67" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="C67" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
     </row>
     <row r="68">
-		</row>
+      <c r="A68" t="s">
+        <v>73</v>
+      </c>
+      <c r="B68" t="s">
+        <v>74</v>
+      </c>
+      <c r="C68" t="s">
+        <v>74</v>
+      </c>
+    </row>
     <row r="69">
-      <c r="A69" t="s">
-        <v>67</v>
-      </c>
       <c r="B69" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="C69" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70">
-		</row>
+      <c r="A70" t="s">
+        <v>75</v>
+      </c>
+      <c r="B70" t="s">
+        <v>42</v>
+      </c>
+      <c r="C70" t="s">
+        <v>42</v>
+      </c>
+    </row>
     <row r="71">
-      <c r="A71" t="s">
-        <v>69</v>
-      </c>
       <c r="B71" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="C71" t="s">
-        <v>70</v>
+        <v>16</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="s">
-        <v>71</v>
-      </c>
-      <c r="B72" t="s">
-        <v>72</v>
-      </c>
-      <c r="C72" t="s">
-        <v>72</v>
-      </c>
-    </row>
+		</row>
     <row r="73">
       <c r="A73" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B73" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C73" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="s">
-        <v>75</v>
-      </c>
-      <c r="B74" t="s">
-        <v>76</v>
-      </c>
-      <c r="C74" t="s">
-        <v>76</v>
-      </c>
-    </row>
+		</row>
     <row r="75">
       <c r="A75" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B75" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C75" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B76" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C76" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B77" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C77" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B78" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C78" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B79" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C79" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B80" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C80" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B81" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C81" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B82" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C82" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="s">
+        <v>94</v>
+      </c>
       <c r="B83" t="s">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="C83" t="s">
-        <v>9</v>
+        <v>95</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B84" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="C84" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="s">
+        <v>98</v>
+      </c>
       <c r="B85" t="s">
-        <v>11</v>
+        <v>99</v>
       </c>
       <c r="C85" t="s">
-        <v>11</v>
+        <v>99</v>
       </c>
     </row>
     <row r="86">
-		</row>
+      <c r="A86" t="s">
+        <v>100</v>
+      </c>
+      <c r="B86" t="s">
+        <v>101</v>
+      </c>
+      <c r="C86" t="s">
+        <v>101</v>
+      </c>
+    </row>
     <row r="87">
-      <c r="A87" t="s">
-        <v>94</v>
+      <c r="B87" t="s">
+        <v>14</v>
+      </c>
+      <c r="C87" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="88">
-		</row>
+      <c r="A88" t="s">
+        <v>102</v>
+      </c>
+      <c r="B88" t="s">
+        <v>77</v>
+      </c>
+      <c r="C88" t="s">
+        <v>77</v>
+      </c>
+    </row>
     <row r="89">
       <c r="B89" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C89" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="s">
-        <v>95</v>
-      </c>
-    </row>
+		</row>
     <row r="91">
-      <c r="B91" t="s">
-        <v>11</v>
-      </c>
-      <c r="C91" t="s">
-        <v>11</v>
+      <c r="A91" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="92">
 		</row>
     <row r="93">
-      <c r="A93" t="s">
-        <v>96</v>
-      </c>
       <c r="B93" t="s">
-        <v>97</v>
+        <v>14</v>
       </c>
       <c r="C93" t="s">
-        <v>97</v>
+        <v>14</v>
       </c>
     </row>
     <row r="94">
-		</row>
+      <c r="A94" t="s">
+        <v>104</v>
+      </c>
+    </row>
     <row r="95">
-      <c r="A95" t="s">
-        <v>98</v>
-      </c>
       <c r="B95" t="s">
-        <v>99</v>
+        <v>16</v>
       </c>
       <c r="C95" t="s">
-        <v>99</v>
+        <v>16</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="s">
-        <v>100</v>
-      </c>
-      <c r="B96" t="s">
-        <v>101</v>
-      </c>
-      <c r="C96" t="s">
-        <v>101</v>
-      </c>
-    </row>
+		</row>
     <row r="97">
       <c r="A97" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B97" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="C97" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="s">
-        <v>104</v>
-      </c>
-      <c r="B98" t="s">
-        <v>105</v>
-      </c>
-      <c r="C98" t="s">
-        <v>105</v>
-      </c>
-    </row>
+		</row>
     <row r="99">
       <c r="A99" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B99" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C99" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="s">
+        <v>109</v>
+      </c>
       <c r="B100" t="s">
-        <v>9</v>
+        <v>110</v>
       </c>
       <c r="C100" t="s">
-        <v>9</v>
+        <v>110</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B101" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
       <c r="C101" t="s">
-        <v>97</v>
+        <v>112</v>
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="s">
+        <v>113</v>
+      </c>
       <c r="B102" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
       <c r="C102" t="s">
-        <v>11</v>
+        <v>114</v>
       </c>
     </row>
     <row r="103">
-		</row>
+      <c r="A103" t="s">
+        <v>115</v>
+      </c>
+      <c r="B103" t="s">
+        <v>116</v>
+      </c>
+      <c r="C103" t="s">
+        <v>116</v>
+      </c>
+    </row>
     <row r="104">
-      <c r="A104" t="s">
-        <v>109</v>
-      </c>
       <c r="B104" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="C104" t="s">
-        <v>110</v>
+        <v>14</v>
       </c>
     </row>
     <row r="105">
-		</row>
+      <c r="A105" t="s">
+        <v>117</v>
+      </c>
+      <c r="B105" t="s">
+        <v>106</v>
+      </c>
+      <c r="C105" t="s">
+        <v>106</v>
+      </c>
+    </row>
     <row r="106">
-      <c r="A106" t="s">
-        <v>111</v>
-      </c>
       <c r="B106" t="s">
-        <v>110</v>
+        <v>16</v>
       </c>
       <c r="C106" t="s">
-        <v>110</v>
+        <v>16</v>
       </c>
     </row>
     <row r="107">
-      <c r="B107" t="s">
-        <v>9</v>
-      </c>
-      <c r="C107" t="s">
-        <v>9</v>
-      </c>
-    </row>
+		</row>
     <row r="108">
       <c r="A108" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B108" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="C108" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="109">
-      <c r="B109" t="s">
-        <v>11</v>
-      </c>
-      <c r="C109" t="s">
-        <v>11</v>
-      </c>
-    </row>
+		</row>
     <row r="110">
+      <c r="A110" t="s">
+        <v>120</v>
+      </c>
       <c r="B110" t="s">
-        <v>9</v>
+        <v>119</v>
       </c>
       <c r="C110" t="s">
-        <v>9</v>
+        <v>119</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="s">
-        <v>113</v>
-      </c>
       <c r="B111" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="C111" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="s">
+        <v>121</v>
+      </c>
       <c r="B112" t="s">
-        <v>11</v>
+        <v>119</v>
       </c>
       <c r="C112" t="s">
-        <v>11</v>
+        <v>119</v>
       </c>
     </row>
     <row r="113">
       <c r="B113" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C113" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="s">
-        <v>114</v>
-      </c>
       <c r="B114" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="C114" t="s">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="115">
-		</row>
+      <c r="A115" t="s">
+        <v>122</v>
+      </c>
+      <c r="B115" t="s">
+        <v>39</v>
+      </c>
+      <c r="C115" t="s">
+        <v>39</v>
+      </c>
+    </row>
     <row r="116">
       <c r="B116" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C116" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="s">
-        <v>115</v>
-      </c>
       <c r="B117" t="s">
-        <v>116</v>
+        <v>14</v>
       </c>
       <c r="C117" t="s">
-        <v>116</v>
+        <v>14</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B118" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
       <c r="C118" t="s">
-        <v>118</v>
+        <v>39</v>
       </c>
     </row>
     <row r="119">
 		</row>
     <row r="120">
-      <c r="A120" t="s">
-        <v>119</v>
-      </c>
       <c r="B120" t="s">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="C120" t="s">
-        <v>118</v>
+        <v>14</v>
       </c>
     </row>
     <row r="121">
-		</row>
+      <c r="A121" t="s">
+        <v>124</v>
+      </c>
+      <c r="B121" t="s">
+        <v>125</v>
+      </c>
+      <c r="C121" t="s">
+        <v>125</v>
+      </c>
+    </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="123">
 		</row>
     <row r="124">
-      <c r="B124" t="s">
-        <v>9</v>
-      </c>
-      <c r="C124" t="s">
-        <v>9</v>
+      <c r="A124" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="s">
-        <v>121</v>
-      </c>
-    </row>
+		</row>
     <row r="126">
-      <c r="B126" t="s">
-        <v>11</v>
-      </c>
-      <c r="C126" t="s">
-        <v>11</v>
+      <c r="A126" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="127">
 		</row>
     <row r="128">
-      <c r="A128" t="s">
-        <v>122</v>
-      </c>
       <c r="B128" t="s">
-        <v>118</v>
+        <v>14</v>
       </c>
       <c r="C128" t="s">
-        <v>118</v>
+        <v>14</v>
       </c>
     </row>
     <row r="129">
-		</row>
+      <c r="A129" t="s">
+        <v>129</v>
+      </c>
+    </row>
     <row r="130">
-      <c r="A130" t="s">
-        <v>123</v>
-      </c>
       <c r="B130" t="s">
-        <v>118</v>
+        <v>16</v>
       </c>
       <c r="C130" t="s">
-        <v>118</v>
+        <v>16</v>
       </c>
     </row>
     <row r="131">
-      <c r="B131" t="s">
-        <v>9</v>
-      </c>
-      <c r="C131" t="s">
-        <v>9</v>
-      </c>
-    </row>
+		</row>
     <row r="132">
       <c r="A132" t="s">
-        <v>124</v>
-      </c>
-      <c r="B132" t="s">
-        <v>118</v>
-      </c>
-      <c r="C132" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
     </row>
     <row r="133">
-      <c r="B133" t="s">
-        <v>11</v>
-      </c>
-      <c r="C133" t="s">
-        <v>11</v>
-      </c>
-    </row>
+		</row>
     <row r="134">
       <c r="B134" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C134" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>125</v>
-      </c>
-      <c r="B135" t="s">
-        <v>118</v>
-      </c>
-      <c r="C135" t="s">
-        <v>118</v>
+        <v>131</v>
       </c>
     </row>
     <row r="136">
       <c r="B136" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C136" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="137">
       <c r="B137" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C137" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>126</v>
-      </c>
-      <c r="B138" t="s">
-        <v>118</v>
-      </c>
-      <c r="C138" t="s">
-        <v>118</v>
+        <v>132</v>
       </c>
     </row>
     <row r="139">
-		</row>
+      <c r="B139" t="s">
+        <v>16</v>
+      </c>
+      <c r="C139" t="s">
+        <v>16</v>
+      </c>
+    </row>
     <row r="140">
       <c r="B140" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C140" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>127</v>
-      </c>
-      <c r="B141" t="s">
-        <v>128</v>
-      </c>
-      <c r="C141" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="s">
-        <v>129</v>
-      </c>
-    </row>
+		</row>
     <row r="143">
-		</row>
+      <c r="B143" t="s">
+        <v>14</v>
+      </c>
+      <c r="C143" t="s">
+        <v>14</v>
+      </c>
+    </row>
     <row r="144">
+      <c r="A144" t="s">
+        <v>134</v>
+      </c>
       <c r="B144" t="s">
-        <v>9</v>
+        <v>125</v>
       </c>
       <c r="C144" t="s">
-        <v>9</v>
+        <v>125</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="146">
 		</row>
     <row r="147">
       <c r="B147" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C147" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>131</v>
-      </c>
-      <c r="B148" t="s">
-        <v>128</v>
-      </c>
-      <c r="C148" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="s">
-        <v>132</v>
-      </c>
-    </row>
+		</row>
     <row r="150">
       <c r="B150" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C150" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>133</v>
+        <v>137</v>
+      </c>
+      <c r="B151" t="s">
+        <v>125</v>
+      </c>
+      <c r="C151" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="152">
-		</row>
+      <c r="A152" t="s">
+        <v>138</v>
+      </c>
+    </row>
     <row r="153">
       <c r="B153" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C153" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="154">
-      <c r="B154" t="s">
-        <v>128</v>
-      </c>
-      <c r="C154" t="s">
-        <v>128</v>
+      <c r="A154" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="s">
-        <v>134</v>
-      </c>
-    </row>
+		</row>
     <row r="156">
       <c r="B156" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C156" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="s">
-        <v>135</v>
+      <c r="B157" t="s">
+        <v>125</v>
+      </c>
+      <c r="C157" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="158">
-		</row>
+      <c r="A158" t="s">
+        <v>140</v>
+      </c>
+    </row>
     <row r="159">
       <c r="B159" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C159" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="160">
-      <c r="B160" t="s">
-        <v>128</v>
-      </c>
-      <c r="C160" t="s">
-        <v>128</v>
+      <c r="A160" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="161">
-      <c r="B161" t="s">
-        <v>136</v>
-      </c>
-      <c r="C161" t="s">
-        <v>136</v>
-      </c>
-    </row>
+		</row>
     <row r="162">
+      <c r="B162" t="s">
+        <v>14</v>
+      </c>
+      <c r="C162" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="s">
+        <v>125</v>
+      </c>
+      <c r="C163" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="B164" t="s">
+        <v>142</v>
+      </c>
+      <c r="C164" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="165">
 		</row>
   </sheetData>
 </worksheet>
